--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104748_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104748_W33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7211</v>
+        <v>2.1776</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4455</v>
+        <v>4.0902</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7244</v>
+        <v>-1.9126</v>
       </c>
       <c r="G2" t="n">
         <v>0.9361</v>
@@ -610,13 +610,13 @@
         <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5574</v>
+        <v>0.0139</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3943</v>
+        <v>0.039</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1631</v>
+        <v>-0.0251</v>
       </c>
       <c r="V2" t="n">
         <v>0.5447</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6123</v>
+        <v>1.344</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8352</v>
+        <v>1.7865</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2229</v>
+        <v>-0.4425</v>
       </c>
       <c r="G3" t="n">
         <v>0.3009</v>
@@ -688,13 +688,13 @@
         <v>0.2276</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5877</v>
+        <v>0.3194</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0926</v>
+        <v>0.0439</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4951</v>
+        <v>0.2755</v>
       </c>
       <c r="V3" t="n">
         <v>1.6342</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1646</v>
+        <v>1.1088</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1615</v>
+        <v>1.2312</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0031</v>
+        <v>-0.1224</v>
       </c>
       <c r="G4" t="n">
         <v>0.6209</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5437</v>
+        <v>0.4879</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3017</v>
+        <v>0.3714</v>
       </c>
       <c r="U4" t="n">
-        <v>0.242</v>
+        <v>0.1165</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.276</v>
+        <v>-0.3734</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5569</v>
+        <v>-0.8425</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2809</v>
+        <v>0.4691</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4558</v>
@@ -844,13 +844,13 @@
         <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2693</v>
+        <v>0.1718</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6731</v>
+        <v>0.3875</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4039</v>
+        <v>-0.2157</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.041</v>
+        <v>-2.4347</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7415</v>
+        <v>-0.9784</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2995</v>
+        <v>-1.4563</v>
       </c>
       <c r="G6" t="n">
         <v>0.5558999999999999</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7689</v>
+        <v>0.3752</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6502</v>
+        <v>0.4133</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1187</v>
+        <v>-0.0381</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0895</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7036</v>
+        <v>-2.7449</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5145</v>
+        <v>-2.3417</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1891</v>
+        <v>-0.4032</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6358</v>
+        <v>-1.8392</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5921</v>
+        <v>-1.5336</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.2279</v>
+        <v>-0.3056</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6151</v>
+        <v>-0.7921</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5406</v>
+        <v>-1.2313</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0745</v>
+        <v>0.4392</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.2508</v>
+        <v>-1.0471</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9485</v>
+        <v>-0.3023</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.3023</v>
+        <v>-0.7447</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4553</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2763</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8211</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2256</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5337</v>
+        <v>-0.4114</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7594</v>
+        <v>0.3463</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.387</v>
+        <v>-0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.387</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0743</v>
+        <v>-2.9385</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7157</v>
+        <v>-1.3604</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3586</v>
+        <v>-1.5781</v>
       </c>
       <c r="G8" t="n">
         <v>-3.1694</v>
@@ -1078,13 +1078,13 @@
         <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0072</v>
+        <v>0.1429</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4182</v>
+        <v>-0.0629</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4254</v>
+        <v>0.2058</v>
       </c>
       <c r="V8" t="n">
         <v>0.3155</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1072</v>
+        <v>-3.0136</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7667</v>
+        <v>-1.1067</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3405</v>
+        <v>-1.9068</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8392</v>
+        <v>-1.6358</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5336</v>
+        <v>0.5921</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3056</v>
+        <v>-2.2279</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7921</v>
+        <v>1.6151</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2313</v>
+        <v>1.5406</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4392</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0471</v>
+        <v>-3.2508</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3023</v>
+        <v>-0.9485</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7447</v>
+        <v>-2.3023</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6829</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1382</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4553</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4274</v>
+        <v>-0.5356</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8364</v>
+        <v>-0.0585</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4091</v>
+        <v>-0.4771</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1578</v>
+        <v>-0.387</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6863</v>
+        <v>-3.2672</v>
       </c>
       <c r="E10" t="n">
-        <v>0.581</v>
+        <v>-0.3643</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.2673</v>
+        <v>-2.9029</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1348</v>
+        <v>-1.501</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5399</v>
+        <v>-1.126</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5948</v>
+        <v>-0.375</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4175</v>
+        <v>0.8299</v>
       </c>
       <c r="K10" t="n">
-        <v>0.71</v>
+        <v>-0.8381</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7075</v>
+        <v>1.668</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.5522</v>
+        <v>-2.3309</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2499</v>
+        <v>-0.2879</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.3023</v>
+        <v>-2.043</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2276</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9105</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0767</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3017</v>
+        <v>-0.0561</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3784</v>
+        <v>-0.0077</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2472</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0093</v>
+        <v>-3.7297</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.075</v>
+        <v>-2.8249</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9343</v>
+        <v>-0.9048</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.501</v>
+        <v>-1.7681</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.126</v>
+        <v>-0.8269</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.375</v>
+        <v>-0.9412</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8299</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8381</v>
+        <v>0.0927</v>
       </c>
       <c r="L11" t="n">
-        <v>1.668</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3309</v>
+        <v>-1.1457</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2879</v>
+        <v>-0.9196</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.043</v>
+        <v>-0.226</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4553</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1382</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6829</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8058</v>
+        <v>-0.8234</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7667</v>
+        <v>-0.0838</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.039</v>
+        <v>-0.7396</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2472</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2472</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.423</v>
+        <v>-3.8291</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2987</v>
+        <v>0.3441</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1244</v>
+        <v>-4.1732</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7681</v>
+        <v>-2.1348</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8269</v>
+        <v>-0.5399</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9412</v>
+        <v>-1.5948</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6225000000000001</v>
+        <v>1.4175</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0927</v>
+        <v>0.71</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7151999999999999</v>
+        <v>0.7075</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1457</v>
+        <v>-3.5522</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9196</v>
+        <v>-1.2499</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.226</v>
+        <v>-2.3023</v>
       </c>
       <c r="P12" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="Q12" t="n">
         <v>-1.1382</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-2.2763</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.1382</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5167</v>
+        <v>-0.2195</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5576</v>
+        <v>0.0648</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9591</v>
+        <v>-0.2843</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1578</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1578</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9167</v>
+        <v>-4.6902</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6361</v>
+        <v>-3.5664</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2806</v>
+        <v>-1.1238</v>
       </c>
       <c r="G13" t="n">
         <v>-2.8706</v>
@@ -1468,13 +1468,13 @@
         <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.5936</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3953</v>
+        <v>-0.3256</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4248</v>
+        <v>-0.268</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3155</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-22.7394</v>
+        <v>-22.3909</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.281900000000001</v>
+        <v>-5.933299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.4576</v>
+        <v>-16.4575</v>
       </c>
       <c r="G14" t="n">
         <v>-13.9609</v>
@@ -1531,7 +1531,7 @@
         <v>-20.8301</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.3263</v>
+        <v>-6.326300000000002</v>
       </c>
       <c r="O14" t="n">
         <v>-14.5035</v>
@@ -1546,13 +1546,13 @@
         <v>10.2435</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1381</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.02689999999999992</v>
+        <v>0.3215999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1112</v>
+        <v>-1.1115</v>
       </c>
       <c r="V14" t="n">
         <v>-1.9498</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2908</v>
+        <v>4.5555</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9317</v>
+        <v>4.079</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3592</v>
+        <v>0.4765</v>
       </c>
       <c r="G15" t="n">
-        <v>4.0341</v>
+        <v>1.2734</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6971</v>
+        <v>-0.4048</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3369</v>
+        <v>1.6783</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5873</v>
+        <v>2.8203</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5546</v>
+        <v>0.3857</v>
       </c>
       <c r="L15" t="n">
-        <v>2.0327</v>
+        <v>2.4346</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4468</v>
+        <v>-1.5469</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1426</v>
+        <v>-0.7906</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3043</v>
+        <v>-0.7563</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6829</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2763</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5934</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0291</v>
+        <v>0.9163</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6207</v>
+        <v>0.1691</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4084</v>
+        <v>0.7471</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0895</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0895</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.787</v>
+        <v>4.0853</v>
       </c>
       <c r="E16" t="n">
-        <v>4.7308</v>
+        <v>1.5879</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0562</v>
+        <v>2.4974</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6924</v>
+        <v>5.767</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2944</v>
+        <v>3.3286</v>
       </c>
       <c r="I16" t="n">
-        <v>0.398</v>
+        <v>2.4384</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0917</v>
+        <v>5.0492</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3097</v>
+        <v>3.344</v>
       </c>
       <c r="L16" t="n">
-        <v>0.782</v>
+        <v>1.7052</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3993</v>
+        <v>0.7178</v>
       </c>
       <c r="N16" t="n">
         <v>-0.0154</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.384</v>
+        <v>0.7331</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0487</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0487</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9776</v>
+        <v>-0.5435</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4813</v>
+        <v>-0.0468</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5037</v>
+        <v>-0.4967</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9317</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1578</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1341</v>
+        <v>3.8151</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2498</v>
+        <v>3.6648</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8843</v>
+        <v>0.1503</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2734</v>
+        <v>2.6924</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4048</v>
+        <v>2.2944</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6783</v>
+        <v>0.398</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8203</v>
+        <v>3.0917</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3857</v>
+        <v>2.3097</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4346</v>
+        <v>0.782</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5469</v>
+        <v>-0.3993</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7906</v>
+        <v>-0.0154</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7563</v>
+        <v>-0.384</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8211</v>
+        <v>2.0487</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8211</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4949</v>
+        <v>0.0057</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.66</v>
+        <v>0.4153</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1549</v>
+        <v>-0.4096</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5447</v>
+        <v>-0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0895</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5447</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.6896</v>
+        <v>3.472</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3372</v>
+        <v>1.8656</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3524</v>
+        <v>1.6064</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8462</v>
+        <v>4.0341</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2786</v>
+        <v>1.6971</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1248</v>
+        <v>2.3369</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8207</v>
+        <v>3.5873</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3685</v>
+        <v>1.5546</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4522</v>
+        <v>2.0327</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9745</v>
+        <v>0.4468</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6471</v>
+        <v>0.1426</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3275</v>
+        <v>0.3043</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1382</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1382</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9117</v>
+        <v>1.2103</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1099</v>
+        <v>0.5547</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8018</v>
+        <v>0.6556</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9317</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5447</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.387</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>A. CARDENAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.3606</v>
+        <v>3.141</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1141</v>
+        <v>4.1258</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2465</v>
+        <v>-0.9849</v>
       </c>
       <c r="G19" t="n">
-        <v>5.767</v>
+        <v>2.1377</v>
       </c>
       <c r="H19" t="n">
-        <v>3.3286</v>
+        <v>-0.0862</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4384</v>
+        <v>2.2239</v>
       </c>
       <c r="J19" t="n">
-        <v>5.0492</v>
+        <v>3.9427</v>
       </c>
       <c r="K19" t="n">
-        <v>3.344</v>
+        <v>0.3308</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7052</v>
+        <v>3.612</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7178</v>
+        <v>-1.805</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0154</v>
+        <v>-0.4169</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7331</v>
+        <v>-1.3881</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1382</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4145</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2763</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2682</v>
+        <v>-0.2927</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5206</v>
+        <v>0.0253</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7476</v>
+        <v>-0.3181</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CARDENAS</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.5974</v>
+        <v>2.6966</v>
       </c>
       <c r="E20" t="n">
-        <v>3.7705</v>
+        <v>1.6265</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1731</v>
+        <v>1.0701</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1377</v>
+        <v>0.8462</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0862</v>
+        <v>-0.2786</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2239</v>
+        <v>1.1248</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9427</v>
+        <v>1.8207</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3308</v>
+        <v>0.3685</v>
       </c>
       <c r="L20" t="n">
-        <v>3.612</v>
+        <v>1.4522</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.805</v>
+        <v>-0.9745</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4169</v>
+        <v>-0.6471</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3881</v>
+        <v>-0.3275</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1382</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
         <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8362000000000001</v>
+        <v>0.9187</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.33</v>
+        <v>0.3992</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5062</v>
+        <v>0.5195</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1578</v>
+        <v>0.9317</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1578</v>
+        <v>0.5447</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3536</v>
+        <v>2.2281</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.402</v>
+        <v>0.1902</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7556</v>
+        <v>2.0379</v>
       </c>
       <c r="G21" t="n">
         <v>1.9667</v>
@@ -2092,13 +2092,13 @@
         <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0197</v>
+        <v>-0.1451</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6785</v>
+        <v>-0.0863</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3412</v>
+        <v>-0.0589</v>
       </c>
       <c r="V21" t="n">
         <v>1.0895</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5978</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5142</v>
+        <v>-0.3814</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9164</v>
+        <v>1.0704</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4638</v>
+        <v>1.1678</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6611</v>
+        <v>0.1225</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8027</v>
+        <v>1.0453</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1998</v>
+        <v>0.8946</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1584</v>
+        <v>0.2101</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3581</v>
+        <v>0.6845</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.264</v>
+        <v>0.2732</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8194</v>
+        <v>-0.0876</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4446</v>
+        <v>0.3608</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4553</v>
+        <v>1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5934</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5851</v>
+        <v>-0.843</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6731</v>
+        <v>-0.5021</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.341</v>
       </c>
       <c r="V22" t="n">
-        <v>2.0212</v>
+        <v>-0.7739</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1789</v>
+        <v>-0.7739</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.027</v>
+        <v>0.4307</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8552</v>
+        <v>1.1588</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8822</v>
+        <v>-0.7282</v>
       </c>
       <c r="G23" t="n">
-        <v>1.1678</v>
+        <v>-2.4638</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1225</v>
+        <v>-0.6611</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0453</v>
+        <v>-1.8027</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8946</v>
+        <v>-0.1998</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2101</v>
+        <v>0.1584</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6845</v>
+        <v>-0.3581</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2732</v>
+        <v>-2.264</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0876</v>
+        <v>-0.8194</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3608</v>
+        <v>-1.4446</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1382</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1382</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.505</v>
+        <v>0.418</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9758</v>
+        <v>0.3178</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5292</v>
+        <v>0.1002</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7739</v>
+        <v>2.0212</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7739</v>
+        <v>2.1789</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0986</v>
+        <v>-2.3739</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9334</v>
+        <v>-1.4596</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1651</v>
+        <v>-0.9142</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4608</v>
@@ -2326,13 +2326,13 @@
         <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2312</v>
+        <v>-0.5064</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6088</v>
+        <v>-0.135</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6224</v>
+        <v>-0.3714</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>22.7393</v>
+        <v>22.7394</v>
       </c>
       <c r="E25" t="n">
-        <v>16.4577</v>
+        <v>16.4576</v>
       </c>
       <c r="F25" t="n">
-        <v>6.2818</v>
+        <v>6.281699999999999</v>
       </c>
       <c r="G25" t="n">
         <v>13.9607</v>
@@ -2380,13 +2380,13 @@
         <v>20.83</v>
       </c>
       <c r="K25" t="n">
-        <v>6.326400000000001</v>
+        <v>6.3264</v>
       </c>
       <c r="L25" t="n">
         <v>14.5037</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.869299999999999</v>
+        <v>-6.869300000000001</v>
       </c>
       <c r="N25" t="n">
         <v>-3.3122</v>
@@ -2404,19 +2404,19 @@
         <v>15.9343</v>
       </c>
       <c r="S25" t="n">
-        <v>1.1381</v>
+        <v>1.1383</v>
       </c>
       <c r="T25" t="n">
-        <v>1.1113</v>
+        <v>1.1112</v>
       </c>
       <c r="U25" t="n">
-        <v>0.02680000000000016</v>
+        <v>0.02669999999999989</v>
       </c>
       <c r="V25" t="n">
         <v>1.9498</v>
       </c>
       <c r="W25" t="n">
-        <v>4.759799999999999</v>
+        <v>4.7598</v>
       </c>
       <c r="X25" t="n">
         <v>-2.81</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104748_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104748_W33.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-4.7597</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104748_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-2.81</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
